--- a/Data/Symbols/edit_variables.xlsx
+++ b/Data/Symbols/edit_variables.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiroaki/Develop/OSS/KSPCompiler/Data/Symbols/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B12385F-8909-2548-928F-96A869063576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034F4A46-AB3D-864E-A9BA-ED74046ABB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-67200" yWindow="-25400" windowWidth="67200" windowHeight="37300" xr2:uid="{6AA66812-27EE-7E42-AA2C-CFF9959C46FD}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,6 +24,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6017" uniqueCount="3013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6041" uniqueCount="3025">
   <si>
     <t>Id</t>
   </si>
@@ -9072,6 +9073,42 @@
   </si>
   <si>
     <t>4737dd0d-bc24-4ed2-bbc8-9360d2250f39</t>
+  </si>
+  <si>
+    <t>$NI_EPP_EQ_MODE_ELECTRIC_C</t>
+  </si>
+  <si>
+    <t>$NI_EPP_TREMOLO_MODE_ELECTRIC_P</t>
+  </si>
+  <si>
+    <t>$ENGINE_PAR_EPP_ELECTRIC_C_BRILLIANT</t>
+  </si>
+  <si>
+    <t>$ENGINE_PAR_EPP_ELECTRIC_C_SOFT</t>
+  </si>
+  <si>
+    <t>$ENGINE_PAR_EPP_ELECTRIC_C_TREBLE</t>
+  </si>
+  <si>
+    <t>$ENGINE_PAR_EPP_ELECTRIC_C_MEDIUM</t>
+  </si>
+  <si>
+    <t>60b345ed-1982-4001-aeb3-0a8fd38312d7</t>
+  </si>
+  <si>
+    <t>3f40741d-63a6-4563-86ce-c53fdb47d6b8</t>
+  </si>
+  <si>
+    <t>f047cb47-b787-4702-9f49-47fa02985424</t>
+  </si>
+  <si>
+    <t>9bc9566d-915c-4610-bc8a-e7e0a6d8fdb9</t>
+  </si>
+  <si>
+    <t>1f96be92-7787-4d20-a2a9-c5b8877dcd66</t>
+  </si>
+  <si>
+    <t>ab1d7072-30ab-40f6-8706-b61710e6e5d9</t>
   </si>
 </sst>
 </file>
@@ -9691,7 +9728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9708,6 +9745,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10085,7 +10128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACEA5FC-45D5-8741-A93D-9D335044AECD}">
-  <dimension ref="A1:E1504"/>
+  <dimension ref="A1:E1510"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
@@ -36932,236 +36975,344 @@
       </c>
     </row>
     <row r="1492" spans="1:5">
-      <c r="A1492" s="4" t="s">
+      <c r="A1492" s="6" t="s">
         <v>3000</v>
       </c>
-      <c r="B1492" s="4" t="s">
+      <c r="B1492" s="6" t="s">
         <v>2987</v>
       </c>
-      <c r="C1492" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1492" s="4" t="str">
+      <c r="C1492" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1492" s="6" t="str">
         <f t="shared" ref="D1492:D1504" si="24">"Built-in Variable: " &amp; B1492</f>
         <v>Built-in Variable: $ENGINE_PAR_FILTER_FEEDBACK_TYPE</v>
       </c>
-      <c r="E1492" s="5" t="s">
+      <c r="E1492" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1493" spans="1:5">
-      <c r="A1493" s="4" t="s">
+      <c r="A1493" s="6" t="s">
         <v>3001</v>
       </c>
-      <c r="B1493" s="4" t="s">
+      <c r="B1493" s="6" t="s">
         <v>2988</v>
       </c>
-      <c r="C1493" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1493" s="4" t="str">
+      <c r="C1493" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1493" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $NI_FILTER_FEEDBACK_TYPE_OFF</v>
       </c>
-      <c r="E1493" s="5" t="s">
+      <c r="E1493" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1494" spans="1:5">
-      <c r="A1494" s="4" t="s">
+      <c r="A1494" s="6" t="s">
         <v>3002</v>
       </c>
-      <c r="B1494" s="4" t="s">
+      <c r="B1494" s="6" t="s">
         <v>2989</v>
       </c>
-      <c r="C1494" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1494" s="4" t="str">
+      <c r="C1494" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1494" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $NI_FILTER_FEEDBACK_TYPE_A</v>
       </c>
-      <c r="E1494" s="5" t="s">
+      <c r="E1494" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1495" spans="1:5">
-      <c r="A1495" s="4" t="s">
+      <c r="A1495" s="6" t="s">
         <v>3003</v>
       </c>
-      <c r="B1495" s="4" t="s">
+      <c r="B1495" s="6" t="s">
         <v>2990</v>
       </c>
-      <c r="C1495" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1495" s="4" t="str">
+      <c r="C1495" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1495" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $NI_FILTER_FEEDBACK_TYPE_B</v>
       </c>
-      <c r="E1495" s="5" t="s">
+      <c r="E1495" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1496" spans="1:5">
-      <c r="A1496" s="4" t="s">
+      <c r="A1496" s="6" t="s">
         <v>3004</v>
       </c>
-      <c r="B1496" s="4" t="s">
+      <c r="B1496" s="6" t="s">
         <v>2991</v>
       </c>
-      <c r="C1496" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1496" s="4" t="str">
+      <c r="C1496" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1496" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_FILTER_FEEDBACK</v>
       </c>
-      <c r="E1496" s="5" t="s">
+      <c r="E1496" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1497" spans="1:5">
-      <c r="A1497" s="4" t="s">
+      <c r="A1497" s="6" t="s">
         <v>3005</v>
       </c>
-      <c r="B1497" s="4" t="s">
+      <c r="B1497" s="6" t="s">
         <v>2992</v>
       </c>
-      <c r="C1497" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1497" s="4" t="str">
+      <c r="C1497" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1497" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_HP_RESONANCE</v>
       </c>
-      <c r="E1497" s="5" t="s">
+      <c r="E1497" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1498" spans="1:5">
-      <c r="A1498" s="4" t="s">
+      <c r="A1498" s="6" t="s">
         <v>3006</v>
       </c>
-      <c r="B1498" s="4" t="s">
+      <c r="B1498" s="6" t="s">
         <v>2993</v>
       </c>
-      <c r="C1498" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1498" s="4" t="str">
+      <c r="C1498" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1498" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_LP_RESONANCE</v>
       </c>
-      <c r="E1498" s="5" t="s">
+      <c r="E1498" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1499" spans="1:5">
-      <c r="A1499" s="4" t="s">
+      <c r="A1499" s="6" t="s">
         <v>3007</v>
       </c>
-      <c r="B1499" s="4" t="s">
+      <c r="B1499" s="6" t="s">
         <v>2994</v>
       </c>
-      <c r="C1499" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1499" s="4" t="str">
+      <c r="C1499" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1499" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_FILTER_FM</v>
       </c>
-      <c r="E1499" s="5" t="s">
+      <c r="E1499" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1500" spans="1:5">
-      <c r="A1500" s="4" t="s">
+      <c r="A1500" s="6" t="s">
         <v>3008</v>
       </c>
-      <c r="B1500" s="4" t="s">
+      <c r="B1500" s="6" t="s">
         <v>2995</v>
       </c>
-      <c r="C1500" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1500" s="4" t="str">
+      <c r="C1500" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1500" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_LP1</v>
       </c>
-      <c r="E1500" s="5" t="s">
+      <c r="E1500" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1501" spans="1:5">
-      <c r="A1501" s="4" t="s">
+      <c r="A1501" s="6" t="s">
         <v>3009</v>
       </c>
-      <c r="B1501" s="4" t="s">
+      <c r="B1501" s="6" t="s">
         <v>2996</v>
       </c>
-      <c r="C1501" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1501" s="4" t="str">
+      <c r="C1501" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1501" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_LP2</v>
       </c>
-      <c r="E1501" s="5" t="s">
+      <c r="E1501" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1502" spans="1:5">
-      <c r="A1502" s="4" t="s">
+      <c r="A1502" s="6" t="s">
         <v>3010</v>
       </c>
-      <c r="B1502" s="4" t="s">
+      <c r="B1502" s="6" t="s">
         <v>2997</v>
       </c>
-      <c r="C1502" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1502" s="4" t="str">
+      <c r="C1502" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1502" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_LP4</v>
       </c>
-      <c r="E1502" s="5" t="s">
+      <c r="E1502" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1503" spans="1:5">
-      <c r="A1503" s="4" t="s">
+      <c r="A1503" s="6" t="s">
         <v>3011</v>
       </c>
-      <c r="B1503" s="4" t="s">
+      <c r="B1503" s="6" t="s">
         <v>2998</v>
       </c>
-      <c r="C1503" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1503" s="4" t="str">
+      <c r="C1503" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1503" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_BP</v>
       </c>
-      <c r="E1503" s="5" t="s">
+      <c r="E1503" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1504" spans="1:5">
-      <c r="A1504" s="4" t="s">
+      <c r="A1504" s="6" t="s">
         <v>3012</v>
       </c>
-      <c r="B1504" s="4" t="s">
+      <c r="B1504" s="6" t="s">
         <v>2999</v>
       </c>
-      <c r="C1504" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1504" s="4" t="str">
+      <c r="C1504" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1504" s="6" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_DUAL_SKF</v>
       </c>
-      <c r="E1504" s="5" t="s">
+      <c r="E1504" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:5">
+      <c r="A1505" s="4" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B1505" s="4" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1505" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1505" s="4" t="str">
+        <f t="shared" ref="D1505:D1510" si="25">"Built-in Variable: " &amp; B1505</f>
+        <v>Built-in Variable: $NI_EPP_EQ_MODE_ELECTRIC_C</v>
+      </c>
+      <c r="E1505" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:5">
+      <c r="A1506" s="4" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B1506" s="4" t="s">
+        <v>3014</v>
+      </c>
+      <c r="C1506" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1506" s="4" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $NI_EPP_TREMOLO_MODE_ELECTRIC_P</v>
+      </c>
+      <c r="E1506" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:5">
+      <c r="A1507" s="4" t="s">
+        <v>3021</v>
+      </c>
+      <c r="B1507" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C1507" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1507" s="4" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $ENGINE_PAR_EPP_ELECTRIC_C_BRILLIANT</v>
+      </c>
+      <c r="E1507" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:5">
+      <c r="A1508" s="4" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B1508" s="4" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C1508" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1508" s="4" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $ENGINE_PAR_EPP_ELECTRIC_C_SOFT</v>
+      </c>
+      <c r="E1508" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:5">
+      <c r="A1509" s="4" t="s">
+        <v>3023</v>
+      </c>
+      <c r="B1509" s="4" t="s">
+        <v>3017</v>
+      </c>
+      <c r="C1509" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1509" s="4" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $ENGINE_PAR_EPP_ELECTRIC_C_TREBLE</v>
+      </c>
+      <c r="E1509" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:5">
+      <c r="A1510" s="4" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B1510" s="4" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C1510" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1510" s="4" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $ENGINE_PAR_EPP_ELECTRIC_C_MEDIUM</v>
+      </c>
+      <c r="E1510" s="5" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Data/Symbols/edit_variables.xlsx
+++ b/Data/Symbols/edit_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hiroaki/Develop/OSS/KSPCompiler/Data/Symbols/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034F4A46-AB3D-864E-A9BA-ED74046ABB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6478BEC-353F-E04C-A572-4EA7D226ADFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-67200" yWindow="-25400" windowWidth="67200" windowHeight="37300" xr2:uid="{6AA66812-27EE-7E42-AA2C-CFF9959C46FD}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6041" uniqueCount="3025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6049" uniqueCount="3029">
   <si>
     <t>Id</t>
   </si>
@@ -9109,6 +9109,20 @@
   </si>
   <si>
     <t>ab1d7072-30ab-40f6-8706-b61710e6e5d9</t>
+  </si>
+  <si>
+    <t>$EVENT_PAR_OUTPUT_TYPE</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>$EVENT_PAR_OUTPUT_INDEX</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ffda7465-938e-4002-bd68-4f892ef1a929</t>
+  </si>
+  <si>
+    <t>fd83d2c6-d672-4c4b-82e3-9c7440ab5270</t>
   </si>
 </sst>
 </file>
@@ -9469,7 +9483,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -9597,6 +9611,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -9728,7 +9753,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9747,10 +9772,7 @@
     <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10128,7 +10150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACEA5FC-45D5-8741-A93D-9D335044AECD}">
-  <dimension ref="A1:E1510"/>
+  <dimension ref="A1:E1512"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
@@ -36975,236 +36997,236 @@
       </c>
     </row>
     <row r="1492" spans="1:5">
-      <c r="A1492" s="6" t="s">
+      <c r="A1492" s="3" t="s">
         <v>3000</v>
       </c>
-      <c r="B1492" s="6" t="s">
+      <c r="B1492" s="3" t="s">
         <v>2987</v>
       </c>
-      <c r="C1492" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1492" s="6" t="str">
+      <c r="C1492" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1492" s="3" t="str">
         <f t="shared" ref="D1492:D1504" si="24">"Built-in Variable: " &amp; B1492</f>
         <v>Built-in Variable: $ENGINE_PAR_FILTER_FEEDBACK_TYPE</v>
       </c>
-      <c r="E1492" s="7" t="s">
+      <c r="E1492" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1493" spans="1:5">
-      <c r="A1493" s="6" t="s">
+      <c r="A1493" s="3" t="s">
         <v>3001</v>
       </c>
-      <c r="B1493" s="6" t="s">
+      <c r="B1493" s="3" t="s">
         <v>2988</v>
       </c>
-      <c r="C1493" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1493" s="6" t="str">
+      <c r="C1493" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1493" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $NI_FILTER_FEEDBACK_TYPE_OFF</v>
       </c>
-      <c r="E1493" s="7" t="s">
+      <c r="E1493" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1494" spans="1:5">
-      <c r="A1494" s="6" t="s">
+      <c r="A1494" s="3" t="s">
         <v>3002</v>
       </c>
-      <c r="B1494" s="6" t="s">
+      <c r="B1494" s="3" t="s">
         <v>2989</v>
       </c>
-      <c r="C1494" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1494" s="6" t="str">
+      <c r="C1494" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1494" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $NI_FILTER_FEEDBACK_TYPE_A</v>
       </c>
-      <c r="E1494" s="7" t="s">
+      <c r="E1494" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1495" spans="1:5">
-      <c r="A1495" s="6" t="s">
+      <c r="A1495" s="3" t="s">
         <v>3003</v>
       </c>
-      <c r="B1495" s="6" t="s">
+      <c r="B1495" s="3" t="s">
         <v>2990</v>
       </c>
-      <c r="C1495" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1495" s="6" t="str">
+      <c r="C1495" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1495" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $NI_FILTER_FEEDBACK_TYPE_B</v>
       </c>
-      <c r="E1495" s="7" t="s">
+      <c r="E1495" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1496" spans="1:5">
-      <c r="A1496" s="6" t="s">
+      <c r="A1496" s="3" t="s">
         <v>3004</v>
       </c>
-      <c r="B1496" s="6" t="s">
+      <c r="B1496" s="3" t="s">
         <v>2991</v>
       </c>
-      <c r="C1496" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1496" s="6" t="str">
+      <c r="C1496" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1496" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_FILTER_FEEDBACK</v>
       </c>
-      <c r="E1496" s="7" t="s">
+      <c r="E1496" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1497" spans="1:5">
-      <c r="A1497" s="6" t="s">
+      <c r="A1497" s="3" t="s">
         <v>3005</v>
       </c>
-      <c r="B1497" s="6" t="s">
+      <c r="B1497" s="3" t="s">
         <v>2992</v>
       </c>
-      <c r="C1497" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1497" s="6" t="str">
+      <c r="C1497" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1497" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_HP_RESONANCE</v>
       </c>
-      <c r="E1497" s="7" t="s">
+      <c r="E1497" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1498" spans="1:5">
-      <c r="A1498" s="6" t="s">
+      <c r="A1498" s="3" t="s">
         <v>3006</v>
       </c>
-      <c r="B1498" s="6" t="s">
+      <c r="B1498" s="3" t="s">
         <v>2993</v>
       </c>
-      <c r="C1498" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1498" s="6" t="str">
+      <c r="C1498" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1498" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_LP_RESONANCE</v>
       </c>
-      <c r="E1498" s="7" t="s">
+      <c r="E1498" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1499" spans="1:5">
-      <c r="A1499" s="6" t="s">
+      <c r="A1499" s="3" t="s">
         <v>3007</v>
       </c>
-      <c r="B1499" s="6" t="s">
+      <c r="B1499" s="3" t="s">
         <v>2994</v>
       </c>
-      <c r="C1499" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1499" s="6" t="str">
+      <c r="C1499" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1499" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $ENGINE_PAR_FILTER_FM</v>
       </c>
-      <c r="E1499" s="7" t="s">
+      <c r="E1499" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1500" spans="1:5">
-      <c r="A1500" s="6" t="s">
+      <c r="A1500" s="3" t="s">
         <v>3008</v>
       </c>
-      <c r="B1500" s="6" t="s">
+      <c r="B1500" s="3" t="s">
         <v>2995</v>
       </c>
-      <c r="C1500" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1500" s="6" t="str">
+      <c r="C1500" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1500" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_LP1</v>
       </c>
-      <c r="E1500" s="7" t="s">
+      <c r="E1500" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1501" spans="1:5">
-      <c r="A1501" s="6" t="s">
+      <c r="A1501" s="3" t="s">
         <v>3009</v>
       </c>
-      <c r="B1501" s="6" t="s">
+      <c r="B1501" s="3" t="s">
         <v>2996</v>
       </c>
-      <c r="C1501" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1501" s="6" t="str">
+      <c r="C1501" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1501" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_LP2</v>
       </c>
-      <c r="E1501" s="7" t="s">
+      <c r="E1501" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1502" spans="1:5">
-      <c r="A1502" s="6" t="s">
+      <c r="A1502" s="3" t="s">
         <v>3010</v>
       </c>
-      <c r="B1502" s="6" t="s">
+      <c r="B1502" s="3" t="s">
         <v>2997</v>
       </c>
-      <c r="C1502" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1502" s="6" t="str">
+      <c r="C1502" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1502" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_LP4</v>
       </c>
-      <c r="E1502" s="7" t="s">
+      <c r="E1502" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1503" spans="1:5">
-      <c r="A1503" s="6" t="s">
+      <c r="A1503" s="3" t="s">
         <v>3011</v>
       </c>
-      <c r="B1503" s="6" t="s">
+      <c r="B1503" s="3" t="s">
         <v>2998</v>
       </c>
-      <c r="C1503" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1503" s="6" t="str">
+      <c r="C1503" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1503" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_MONARK_BP</v>
       </c>
-      <c r="E1503" s="7" t="s">
+      <c r="E1503" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="1504" spans="1:5">
-      <c r="A1504" s="6" t="s">
+      <c r="A1504" s="3" t="s">
         <v>3012</v>
       </c>
-      <c r="B1504" s="6" t="s">
+      <c r="B1504" s="3" t="s">
         <v>2999</v>
       </c>
-      <c r="C1504" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1504" s="6" t="str">
+      <c r="C1504" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1504" s="3" t="str">
         <f t="shared" si="24"/>
         <v>Built-in Variable: $FILTER_TYPE_DUAL_SKF</v>
       </c>
-      <c r="E1504" s="7" t="s">
+      <c r="E1504" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37219,7 +37241,7 @@
         <v>6</v>
       </c>
       <c r="D1505" s="4" t="str">
-        <f t="shared" ref="D1505:D1510" si="25">"Built-in Variable: " &amp; B1505</f>
+        <f t="shared" ref="D1505:D1512" si="25">"Built-in Variable: " &amp; B1505</f>
         <v>Built-in Variable: $NI_EPP_EQ_MODE_ELECTRIC_C</v>
       </c>
       <c r="E1505" s="5" t="s">
@@ -37313,6 +37335,42 @@
         <v>Built-in Variable: $ENGINE_PAR_EPP_ELECTRIC_C_MEDIUM</v>
       </c>
       <c r="E1510" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:5">
+      <c r="A1511" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B1511" s="6" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C1511" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1511" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $EVENT_PAR_OUTPUT_TYPE</v>
+      </c>
+      <c r="E1511" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:5">
+      <c r="A1512" t="s">
+        <v>3028</v>
+      </c>
+      <c r="B1512" s="6" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C1512" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1512" s="6" t="str">
+        <f t="shared" si="25"/>
+        <v>Built-in Variable: $EVENT_PAR_OUTPUT_INDEX</v>
+      </c>
+      <c r="E1512" s="5" t="s">
         <v>7</v>
       </c>
     </row>
